--- a/output/StructureDefinition-t-cabs-observation-druck-minmax.xlsx
+++ b/output/StructureDefinition-t-cabs-observation-druck-minmax.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-20T17:13:04+01:00</t>
+    <t>2025-11-21T13:42:11+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-observation-druck-minmax.xlsx
+++ b/output/StructureDefinition-t-cabs-observation-druck-minmax.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-25T10:29:35+01:00</t>
+    <t>2025-12-09T09:55:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-observation-druck-minmax.xlsx
+++ b/output/StructureDefinition-t-cabs-observation-druck-minmax.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7612" uniqueCount="765">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7612" uniqueCount="768">
   <si>
     <t>Property</t>
   </si>
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://t-cabs.org/StructureDefinition/t-cabs-observation-druck-minmax</t>
+    <t>https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-observation-druck-minmax</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-09T09:55:43+01:00</t>
+    <t>2026-02-19T13:21:58+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://t-cabs.org/StructureDefinition/t-cabs-observation-beatmungsparametermitkomponenten</t>
+    <t>https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-observation-beatmungsparametermitkomponenten</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -713,7 +713,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-procedure-beatmung)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-procedure-beatmung)
 </t>
   </si>
   <si>
@@ -875,7 +875,7 @@
     <t>Code defined by a terminology system</t>
   </si>
   <si>
-    <t>A reference to a code defined by a terminology system.</t>
+    <t>Pressure of gas in airway.</t>
   </si>
   <si>
     <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
@@ -1050,7 +1050,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-patient)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-patient)
 </t>
   </si>
   <si>
@@ -1526,7 +1526,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-devicemetric-numericmetric)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-devicemetric-numericmetric)
 </t>
   </si>
   <si>
@@ -1987,6 +1987,9 @@
     <t>Observation.component.code.coding</t>
   </si>
   <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
     <t>Observation.component.code.coding.id</t>
   </si>
   <si>
@@ -2184,7 +2187,6 @@
   &lt;coding&gt;
     &lt;system value="urn:iso:std:iso:11073:10101"/&gt;
     &lt;code value="151794"/&gt;
-    &lt;display value="MDC_PRESS_AWAY_MIN"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -2196,6 +2198,9 @@
   </si>
   <si>
     <t>Observation.component:MinPress.code.coding</t>
+  </si>
+  <si>
+    <t>Minimum pressure of gas in airway.</t>
   </si>
   <si>
     <t>Observation.component:MinPress.code.coding.id</t>
@@ -2310,7 +2315,6 @@
   &lt;coding&gt;
     &lt;system value="urn:iso:std:iso:11073:10101"/&gt;
     &lt;code value="151793"/&gt;
-    &lt;display value="MDC_PRESS_AWAY_MAX"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -2322,6 +2326,9 @@
   </si>
   <si>
     <t>Observation.component:MaxPress.code.coding</t>
+  </si>
+  <si>
+    <t>Peak pressure of gas in airway.</t>
   </si>
   <si>
     <t>Observation.component:MaxPress.code.coding.id</t>
@@ -13797,7 +13804,7 @@
         <v>273</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>274</v>
+        <v>629</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>275</v>
@@ -13890,10 +13897,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14011,10 +14018,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14134,10 +14141,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14259,10 +14266,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14382,10 +14389,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14482,7 +14489,7 @@
         <v>106</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>83</v>
@@ -14505,10 +14512,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14628,10 +14635,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14753,10 +14760,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14878,10 +14885,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14904,16 +14911,16 @@
         <v>95</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M99" t="s" s="2">
         <v>418</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="O99" t="s" s="2">
         <v>420</v>
@@ -14963,7 +14970,7 @@
         <v>364</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14972,7 +14979,7 @@
         <v>94</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>106</v>
@@ -14984,7 +14991,7 @@
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>423</v>
@@ -15001,13 +15008,13 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>83</v>
@@ -15029,16 +15036,16 @@
         <v>95</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M100" t="s" s="2">
         <v>418</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="O100" t="s" s="2">
         <v>420</v>
@@ -15090,7 +15097,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -15111,7 +15118,7 @@
         <v>83</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>423</v>
@@ -15128,10 +15135,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15249,10 +15256,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15372,10 +15379,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15474,7 +15481,7 @@
         <v>106</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>83</v>
@@ -15497,10 +15504,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15529,7 +15536,7 @@
         <v>527</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
@@ -15622,10 +15629,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15745,10 +15752,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15868,10 +15875,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15970,7 +15977,7 @@
         <v>106</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>83</v>
@@ -15993,10 +16000,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16022,13 +16029,13 @@
         <v>244</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="O108" t="s" s="2">
         <v>430</v>
@@ -16080,7 +16087,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -16089,7 +16096,7 @@
         <v>94</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>106</v>
@@ -16118,10 +16125,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16185,25 +16192,25 @@
       </c>
       <c r="Y109" s="2"/>
       <c r="Z109" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF109" t="s" s="2">
         <v>669</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>668</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -16241,10 +16248,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16270,10 +16277,10 @@
         <v>493</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N110" t="s" s="2">
         <v>496</v>
@@ -16328,7 +16335,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -16366,10 +16373,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16487,10 +16494,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16610,10 +16617,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16735,10 +16742,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16764,7 +16771,7 @@
         <v>509</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="M114" t="s" s="2">
         <v>511</v>
@@ -16833,7 +16840,7 @@
         <v>106</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>83</v>
@@ -16856,10 +16863,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16885,7 +16892,7 @@
         <v>509</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M115" t="s" s="2">
         <v>560</v>
@@ -16954,7 +16961,7 @@
         <v>106</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>83</v>
@@ -16977,10 +16984,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17102,10 +17109,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17227,10 +17234,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17350,10 +17357,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17471,13 +17478,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>609</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D120" t="s" s="2">
         <v>83</v>
@@ -17598,7 +17605,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>618</v>
@@ -17719,7 +17726,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>619</v>
@@ -17842,7 +17849,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>620</v>
@@ -17967,7 +17974,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>621</v>
@@ -18015,7 +18022,7 @@
         <v>83</v>
       </c>
       <c r="S124" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="T124" t="s" s="2">
         <v>83</v>
@@ -18090,7 +18097,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>626</v>
@@ -18211,7 +18218,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>627</v>
@@ -18334,7 +18341,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>628</v>
@@ -18366,7 +18373,7 @@
         <v>273</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>274</v>
+        <v>697</v>
       </c>
       <c r="N127" t="s" s="2">
         <v>275</v>
@@ -18459,10 +18466,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18580,10 +18587,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18703,10 +18710,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18828,10 +18835,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18951,10 +18958,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19051,7 +19058,7 @@
         <v>106</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>83</v>
@@ -19074,10 +19081,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19197,10 +19204,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19322,10 +19329,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19447,10 +19454,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19473,16 +19480,16 @@
         <v>95</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M136" t="s" s="2">
         <v>418</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="O136" t="s" s="2">
         <v>420</v>
@@ -19532,7 +19539,7 @@
         <v>364</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -19541,7 +19548,7 @@
         <v>94</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AJ136" t="s" s="2">
         <v>106</v>
@@ -19553,7 +19560,7 @@
         <v>83</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>423</v>
@@ -19570,13 +19577,13 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>83</v>
@@ -19598,16 +19605,16 @@
         <v>95</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M137" t="s" s="2">
         <v>418</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="O137" t="s" s="2">
         <v>420</v>
@@ -19659,7 +19666,7 @@
         <v>83</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -19680,7 +19687,7 @@
         <v>83</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>423</v>
@@ -19697,10 +19704,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19818,10 +19825,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19941,10 +19948,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20043,7 +20050,7 @@
         <v>106</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>83</v>
@@ -20066,10 +20073,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20098,7 +20105,7 @@
         <v>527</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
@@ -20191,10 +20198,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20237,7 +20244,7 @@
         <v>83</v>
       </c>
       <c r="S142" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="T142" t="s" s="2">
         <v>83</v>
@@ -20314,10 +20321,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20437,10 +20444,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20485,7 +20492,7 @@
         <v>83</v>
       </c>
       <c r="S144" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="T144" t="s" s="2">
         <v>83</v>
@@ -20539,7 +20546,7 @@
         <v>106</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AL144" t="s" s="2">
         <v>83</v>
@@ -20562,10 +20569,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20591,13 +20598,13 @@
         <v>244</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="O145" t="s" s="2">
         <v>430</v>
@@ -20649,7 +20656,7 @@
         <v>83</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>81</v>
@@ -20658,7 +20665,7 @@
         <v>94</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AJ145" t="s" s="2">
         <v>106</v>
@@ -20687,10 +20694,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20754,25 +20761,25 @@
       </c>
       <c r="Y146" s="2"/>
       <c r="Z146" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF146" t="s" s="2">
         <v>669</v>
-      </c>
-      <c r="AA146" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB146" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC146" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD146" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE146" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF146" t="s" s="2">
-        <v>668</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>81</v>
@@ -20810,10 +20817,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20839,10 +20846,10 @@
         <v>493</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N147" t="s" s="2">
         <v>496</v>
@@ -20897,7 +20904,7 @@
         <v>83</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>81</v>
@@ -20935,10 +20942,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21056,10 +21063,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21179,10 +21186,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -21304,10 +21311,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21333,7 +21340,7 @@
         <v>509</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="M151" t="s" s="2">
         <v>511</v>
@@ -21402,7 +21409,7 @@
         <v>106</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AL151" t="s" s="2">
         <v>83</v>
@@ -21425,10 +21432,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -21454,7 +21461,7 @@
         <v>509</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M152" t="s" s="2">
         <v>560</v>
@@ -21523,7 +21530,7 @@
         <v>106</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AL152" t="s" s="2">
         <v>83</v>
@@ -21546,10 +21553,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21671,10 +21678,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21796,10 +21803,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21919,10 +21926,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -22040,13 +22047,13 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>609</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="D157" t="s" s="2">
         <v>83</v>
@@ -22167,7 +22174,7 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>618</v>
@@ -22288,7 +22295,7 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>619</v>
@@ -22411,7 +22418,7 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>620</v>
@@ -22536,7 +22543,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>621</v>
@@ -22584,7 +22591,7 @@
         <v>83</v>
       </c>
       <c r="S161" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="T161" t="s" s="2">
         <v>83</v>
@@ -22659,7 +22666,7 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>626</v>
@@ -22780,7 +22787,7 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>627</v>
@@ -22903,7 +22910,7 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>628</v>
@@ -22935,7 +22942,7 @@
         <v>273</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>274</v>
+        <v>738</v>
       </c>
       <c r="N164" t="s" s="2">
         <v>275</v>
@@ -23028,10 +23035,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -23149,10 +23156,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -23272,10 +23279,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -23397,10 +23404,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23520,10 +23527,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23620,7 +23627,7 @@
         <v>106</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AL169" t="s" s="2">
         <v>83</v>
@@ -23643,10 +23650,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23766,10 +23773,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23891,10 +23898,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -24016,10 +24023,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -24042,16 +24049,16 @@
         <v>95</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M173" t="s" s="2">
         <v>418</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="O173" t="s" s="2">
         <v>420</v>
@@ -24101,7 +24108,7 @@
         <v>364</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>81</v>
@@ -24110,7 +24117,7 @@
         <v>94</v>
       </c>
       <c r="AI173" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AJ173" t="s" s="2">
         <v>106</v>
@@ -24122,7 +24129,7 @@
         <v>83</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AN173" t="s" s="2">
         <v>423</v>
@@ -24139,13 +24146,13 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D174" t="s" s="2">
         <v>83</v>
@@ -24167,16 +24174,16 @@
         <v>95</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M174" t="s" s="2">
         <v>418</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="O174" t="s" s="2">
         <v>420</v>
@@ -24228,7 +24235,7 @@
         <v>83</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>81</v>
@@ -24249,7 +24256,7 @@
         <v>83</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AN174" t="s" s="2">
         <v>423</v>
@@ -24266,10 +24273,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -24387,10 +24394,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -24510,10 +24517,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24612,7 +24619,7 @@
         <v>106</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AL177" t="s" s="2">
         <v>83</v>
@@ -24635,10 +24642,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24667,7 +24674,7 @@
         <v>527</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" t="s" s="2">
@@ -24760,10 +24767,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24806,7 +24813,7 @@
         <v>83</v>
       </c>
       <c r="S179" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="T179" t="s" s="2">
         <v>83</v>
@@ -24883,10 +24890,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -25006,10 +25013,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -25054,7 +25061,7 @@
         <v>83</v>
       </c>
       <c r="S181" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="T181" t="s" s="2">
         <v>83</v>
@@ -25108,7 +25115,7 @@
         <v>106</v>
       </c>
       <c r="AK181" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AL181" t="s" s="2">
         <v>83</v>
@@ -25131,10 +25138,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -25160,13 +25167,13 @@
         <v>244</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="O182" t="s" s="2">
         <v>430</v>
@@ -25218,7 +25225,7 @@
         <v>83</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>81</v>
@@ -25227,7 +25234,7 @@
         <v>94</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AJ182" t="s" s="2">
         <v>106</v>
@@ -25256,10 +25263,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -25323,25 +25330,25 @@
       </c>
       <c r="Y183" s="2"/>
       <c r="Z183" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="AA183" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB183" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC183" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD183" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE183" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF183" t="s" s="2">
         <v>669</v>
-      </c>
-      <c r="AA183" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB183" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC183" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD183" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE183" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF183" t="s" s="2">
-        <v>668</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>81</v>
@@ -25379,10 +25386,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25408,10 +25415,10 @@
         <v>493</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N184" t="s" s="2">
         <v>496</v>
@@ -25466,7 +25473,7 @@
         <v>83</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>81</v>
@@ -25504,10 +25511,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25625,10 +25632,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25748,10 +25755,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25873,10 +25880,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25902,7 +25909,7 @@
         <v>509</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="M188" t="s" s="2">
         <v>511</v>
@@ -25971,7 +25978,7 @@
         <v>106</v>
       </c>
       <c r="AK188" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AL188" t="s" s="2">
         <v>83</v>
@@ -25994,10 +26001,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -26023,7 +26030,7 @@
         <v>509</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M189" t="s" s="2">
         <v>560</v>
@@ -26092,7 +26099,7 @@
         <v>106</v>
       </c>
       <c r="AK189" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AL189" t="s" s="2">
         <v>83</v>
@@ -26115,10 +26122,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -26240,10 +26247,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -26365,10 +26372,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -26488,10 +26495,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
